--- a/artfynd/A 21236-2021 artfynd.xlsx
+++ b/artfynd/A 21236-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21236-2021 artfynd.xlsx
+++ b/artfynd/A 21236-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3327,6 +3327,558 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>115823420</v>
+      </c>
+      <c r="B23" t="n">
+        <v>83201</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skogen NÖ om Sylbergen, Skogen NÖ om Sylbergen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>559055</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6632778</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Mossig äldre granskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Pia Hagfors, Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>115823561</v>
+      </c>
+      <c r="B24" t="n">
+        <v>83201</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skogen NÖ om Sylbergen, Skogen NÖ om Sylbergen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>559064</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6632776</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Äldre mossig granskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Pia Hagfors, Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>115823361</v>
+      </c>
+      <c r="B25" t="n">
+        <v>83201</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skogen NÖ om Sylbergen, Skogen NÖ om Sylbergen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>559058</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6632778</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Äldre mossig granskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Pia Hagfors, Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>115823260</v>
+      </c>
+      <c r="B26" t="n">
+        <v>83201</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Skogen NÖ om Sylbergen, Skogen NÖ om Sylbergen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>559057</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6632778</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Pia Hagfors, Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21236-2021 artfynd.xlsx
+++ b/artfynd/A 21236-2021 artfynd.xlsx
@@ -3329,7 +3329,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115823420</v>
+        <v>115823260</v>
       </c>
       <c r="B23" t="n">
         <v>83201</v>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3380,13 +3380,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559055</v>
+        <v>559057</v>
       </c>
       <c r="R23" t="n">
         <v>6632778</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Mossig äldre granskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3467,7 +3467,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115823561</v>
+        <v>115823361</v>
       </c>
       <c r="B24" t="n">
         <v>83201</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3518,13 +3518,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559064</v>
+        <v>559058</v>
       </c>
       <c r="R24" t="n">
-        <v>6632776</v>
+        <v>6632778</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3605,7 +3605,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115823361</v>
+        <v>115823561</v>
       </c>
       <c r="B25" t="n">
         <v>83201</v>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3656,13 +3656,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559058</v>
+        <v>559064</v>
       </c>
       <c r="R25" t="n">
-        <v>6632778</v>
+        <v>6632776</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3743,7 +3743,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115823260</v>
+        <v>115823420</v>
       </c>
       <c r="B26" t="n">
         <v>83201</v>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3794,13 +3794,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>559057</v>
+        <v>559055</v>
       </c>
       <c r="R26" t="n">
         <v>6632778</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Mossig äldre granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 21236-2021 artfynd.xlsx
+++ b/artfynd/A 21236-2021 artfynd.xlsx
@@ -3329,7 +3329,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115823260</v>
+        <v>115823361</v>
       </c>
       <c r="B23" t="n">
         <v>83201</v>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3380,13 +3380,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559057</v>
+        <v>559058</v>
       </c>
       <c r="R23" t="n">
         <v>6632778</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Äldre mossig granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3467,7 +3467,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115823361</v>
+        <v>115823260</v>
       </c>
       <c r="B24" t="n">
         <v>83201</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3518,13 +3518,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559058</v>
+        <v>559057</v>
       </c>
       <c r="R24" t="n">
         <v>6632778</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Äldre mossig granskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 21236-2021 artfynd.xlsx
+++ b/artfynd/A 21236-2021 artfynd.xlsx
@@ -3329,7 +3329,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115823361</v>
+        <v>115823420</v>
       </c>
       <c r="B23" t="n">
         <v>83201</v>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3380,13 +3380,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559058</v>
+        <v>559055</v>
       </c>
       <c r="R23" t="n">
         <v>6632778</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Äldre mossig granskog</t>
+          <t>Mossig äldre granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3467,7 +3467,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115823260</v>
+        <v>115823361</v>
       </c>
       <c r="B24" t="n">
         <v>83201</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3518,13 +3518,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559057</v>
+        <v>559058</v>
       </c>
       <c r="R24" t="n">
         <v>6632778</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Äldre mossig granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3743,7 +3743,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115823420</v>
+        <v>115823260</v>
       </c>
       <c r="B26" t="n">
         <v>83201</v>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3794,13 +3794,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>559055</v>
+        <v>559057</v>
       </c>
       <c r="R26" t="n">
         <v>6632778</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Mossig äldre granskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 21236-2021 artfynd.xlsx
+++ b/artfynd/A 21236-2021 artfynd.xlsx
@@ -3467,7 +3467,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115823361</v>
+        <v>115823561</v>
       </c>
       <c r="B24" t="n">
         <v>83201</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3518,13 +3518,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559058</v>
+        <v>559064</v>
       </c>
       <c r="R24" t="n">
-        <v>6632778</v>
+        <v>6632776</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3605,7 +3605,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115823561</v>
+        <v>115823260</v>
       </c>
       <c r="B25" t="n">
         <v>83201</v>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3656,13 +3656,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559064</v>
+        <v>559057</v>
       </c>
       <c r="R25" t="n">
-        <v>6632776</v>
+        <v>6632778</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Äldre mossig granskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3743,7 +3743,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115823260</v>
+        <v>115823361</v>
       </c>
       <c r="B26" t="n">
         <v>83201</v>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3794,13 +3794,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>559057</v>
+        <v>559058</v>
       </c>
       <c r="R26" t="n">
         <v>6632778</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Äldre mossig granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 21236-2021 artfynd.xlsx
+++ b/artfynd/A 21236-2021 artfynd.xlsx
@@ -3332,7 +3332,7 @@
         <v>115823420</v>
       </c>
       <c r="B23" t="n">
-        <v>83201</v>
+        <v>83208</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115823561</v>
+        <v>115823260</v>
       </c>
       <c r="B24" t="n">
-        <v>83201</v>
+        <v>83208</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3518,13 +3518,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559064</v>
+        <v>559057</v>
       </c>
       <c r="R24" t="n">
-        <v>6632776</v>
+        <v>6632778</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Äldre mossig granskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3605,10 +3605,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115823260</v>
+        <v>115823361</v>
       </c>
       <c r="B25" t="n">
-        <v>83201</v>
+        <v>83208</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3656,13 +3656,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559057</v>
+        <v>559058</v>
       </c>
       <c r="R25" t="n">
         <v>6632778</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Äldre mossig granskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3743,10 +3743,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115823361</v>
+        <v>115823561</v>
       </c>
       <c r="B26" t="n">
-        <v>83201</v>
+        <v>83208</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3794,13 +3794,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>559058</v>
+        <v>559064</v>
       </c>
       <c r="R26" t="n">
-        <v>6632778</v>
+        <v>6632776</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 21236-2021 artfynd.xlsx
+++ b/artfynd/A 21236-2021 artfynd.xlsx
@@ -3329,7 +3329,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115823420</v>
+        <v>115823260</v>
       </c>
       <c r="B23" t="n">
         <v>83208</v>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3380,13 +3380,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559055</v>
+        <v>559057</v>
       </c>
       <c r="R23" t="n">
         <v>6632778</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Mossig äldre granskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3605,7 +3605,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115823260</v>
+        <v>115823420</v>
       </c>
       <c r="B25" t="n">
         <v>83208</v>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3656,13 +3656,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559057</v>
+        <v>559055</v>
       </c>
       <c r="R25" t="n">
         <v>6632778</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Mossig äldre granskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>

--- a/artfynd/A 21236-2021 artfynd.xlsx
+++ b/artfynd/A 21236-2021 artfynd.xlsx
@@ -3329,7 +3329,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115823260</v>
+        <v>115823561</v>
       </c>
       <c r="B23" t="n">
         <v>83208</v>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3380,13 +3380,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559057</v>
+        <v>559064</v>
       </c>
       <c r="R23" t="n">
-        <v>6632778</v>
+        <v>6632776</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Äldre mossig granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3467,7 +3467,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115823561</v>
+        <v>115823420</v>
       </c>
       <c r="B24" t="n">
         <v>83208</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559064</v>
+        <v>559055</v>
       </c>
       <c r="R24" t="n">
-        <v>6632776</v>
+        <v>6632778</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Äldre mossig granskog</t>
+          <t>Mossig äldre granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3605,7 +3605,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115823420</v>
+        <v>115823260</v>
       </c>
       <c r="B25" t="n">
         <v>83208</v>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3656,13 +3656,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559055</v>
+        <v>559057</v>
       </c>
       <c r="R25" t="n">
         <v>6632778</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Mossig äldre granskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>

--- a/artfynd/A 21236-2021 artfynd.xlsx
+++ b/artfynd/A 21236-2021 artfynd.xlsx
@@ -3329,7 +3329,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115823561</v>
+        <v>115823260</v>
       </c>
       <c r="B23" t="n">
         <v>83208</v>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3380,13 +3380,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559064</v>
+        <v>559057</v>
       </c>
       <c r="R23" t="n">
-        <v>6632776</v>
+        <v>6632778</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Äldre mossig granskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3467,7 +3467,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115823420</v>
+        <v>115823361</v>
       </c>
       <c r="B24" t="n">
         <v>83208</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3518,13 +3518,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559055</v>
+        <v>559058</v>
       </c>
       <c r="R24" t="n">
         <v>6632778</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Mossig äldre granskog</t>
+          <t>Äldre mossig granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3605,7 +3605,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115823260</v>
+        <v>115823561</v>
       </c>
       <c r="B25" t="n">
         <v>83208</v>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3656,13 +3656,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559057</v>
+        <v>559064</v>
       </c>
       <c r="R25" t="n">
-        <v>6632778</v>
+        <v>6632776</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Äldre mossig granskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3743,7 +3743,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115823361</v>
+        <v>115823420</v>
       </c>
       <c r="B26" t="n">
         <v>83208</v>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3794,13 +3794,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>559058</v>
+        <v>559055</v>
       </c>
       <c r="R26" t="n">
         <v>6632778</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Äldre mossig granskog</t>
+          <t>Mossig äldre granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 21236-2021 artfynd.xlsx
+++ b/artfynd/A 21236-2021 artfynd.xlsx
@@ -3329,7 +3329,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115823260</v>
+        <v>115823561</v>
       </c>
       <c r="B23" t="n">
         <v>83208</v>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3380,13 +3380,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559057</v>
+        <v>559064</v>
       </c>
       <c r="R23" t="n">
-        <v>6632778</v>
+        <v>6632776</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Äldre mossig granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3467,7 +3467,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115823361</v>
+        <v>115823260</v>
       </c>
       <c r="B24" t="n">
         <v>83208</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3518,13 +3518,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559058</v>
+        <v>559057</v>
       </c>
       <c r="R24" t="n">
         <v>6632778</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Äldre mossig granskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3605,7 +3605,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115823561</v>
+        <v>115823420</v>
       </c>
       <c r="B25" t="n">
         <v>83208</v>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559064</v>
+        <v>559055</v>
       </c>
       <c r="R25" t="n">
-        <v>6632776</v>
+        <v>6632778</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Äldre mossig granskog</t>
+          <t>Mossig äldre granskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3743,7 +3743,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115823420</v>
+        <v>115823361</v>
       </c>
       <c r="B26" t="n">
         <v>83208</v>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3794,13 +3794,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>559055</v>
+        <v>559058</v>
       </c>
       <c r="R26" t="n">
         <v>6632778</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Mossig äldre granskog</t>
+          <t>Äldre mossig granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 21236-2021 artfynd.xlsx
+++ b/artfynd/A 21236-2021 artfynd.xlsx
@@ -3329,7 +3329,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115823561</v>
+        <v>115823361</v>
       </c>
       <c r="B23" t="n">
         <v>83208</v>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3380,13 +3380,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559064</v>
+        <v>559058</v>
       </c>
       <c r="R23" t="n">
-        <v>6632776</v>
+        <v>6632778</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3743,7 +3743,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115823361</v>
+        <v>115823561</v>
       </c>
       <c r="B26" t="n">
         <v>83208</v>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3794,13 +3794,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>559058</v>
+        <v>559064</v>
       </c>
       <c r="R26" t="n">
-        <v>6632778</v>
+        <v>6632776</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 21236-2021 artfynd.xlsx
+++ b/artfynd/A 21236-2021 artfynd.xlsx
@@ -3467,7 +3467,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115823260</v>
+        <v>115823561</v>
       </c>
       <c r="B24" t="n">
         <v>83208</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3518,13 +3518,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559057</v>
+        <v>559064</v>
       </c>
       <c r="R24" t="n">
-        <v>6632778</v>
+        <v>6632776</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Äldre mossig granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3743,7 +3743,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115823561</v>
+        <v>115823260</v>
       </c>
       <c r="B26" t="n">
         <v>83208</v>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3794,13 +3794,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>559064</v>
+        <v>559057</v>
       </c>
       <c r="R26" t="n">
-        <v>6632776</v>
+        <v>6632778</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Äldre mossig granskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 21236-2021 artfynd.xlsx
+++ b/artfynd/A 21236-2021 artfynd.xlsx
@@ -3329,10 +3329,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115823361</v>
+        <v>115823420</v>
       </c>
       <c r="B23" t="n">
-        <v>83208</v>
+        <v>83222</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3380,13 +3380,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559058</v>
+        <v>559055</v>
       </c>
       <c r="R23" t="n">
         <v>6632778</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Äldre mossig granskog</t>
+          <t>Mossig äldre granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115823561</v>
+        <v>115823361</v>
       </c>
       <c r="B24" t="n">
-        <v>83208</v>
+        <v>83222</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3518,13 +3518,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559064</v>
+        <v>559058</v>
       </c>
       <c r="R24" t="n">
-        <v>6632776</v>
+        <v>6632778</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3605,10 +3605,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115823420</v>
+        <v>115823260</v>
       </c>
       <c r="B25" t="n">
-        <v>83208</v>
+        <v>83222</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3656,13 +3656,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559055</v>
+        <v>559057</v>
       </c>
       <c r="R25" t="n">
         <v>6632778</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Mossig äldre granskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3743,10 +3743,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115823260</v>
+        <v>115823561</v>
       </c>
       <c r="B26" t="n">
-        <v>83208</v>
+        <v>83222</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3794,13 +3794,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>559057</v>
+        <v>559064</v>
       </c>
       <c r="R26" t="n">
-        <v>6632778</v>
+        <v>6632776</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Äldre mossig granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
